--- a/public/plantilla-com-recepcion.xlsx
+++ b/public/plantilla-com-recepcion.xlsx
@@ -16,9 +16,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
-    <numFmt numFmtId="165" formatCode="0.0"/>
-    <numFmt numFmtId="166" formatCode="0.0%"/>
-    <numFmt numFmtId="167" formatCode="hh:mm"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
+    <numFmt numFmtId="166" formatCode="hh:mm"/>
   </numFmts>
   <fonts count="26">
     <font>
@@ -196,7 +196,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="18">
+  <fills count="19">
     <fill>
       <patternFill/>
     </fill>
@@ -294,6 +294,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6FAFE"/>
       </patternFill>
     </fill>
   </fills>
@@ -599,7 +604,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="188">
+  <cellXfs count="195">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center"/>
@@ -724,34 +729,34 @@
     <xf numFmtId="14" fontId="6" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="18" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="5" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="166" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="1" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="10" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
@@ -937,7 +942,7 @@
     <xf numFmtId="0" fontId="12" fillId="9" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="21" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
@@ -946,7 +951,7 @@
     <xf numFmtId="0" fontId="20" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="20" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="164" fontId="20" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="6" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
@@ -967,28 +972,28 @@
     <xf numFmtId="9" fontId="20" fillId="6" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="19" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="21" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="166" fontId="19" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="21" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="1" fontId="19" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="19" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="20" fillId="6" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="164" fontId="20" fillId="6" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="10" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
@@ -1101,11 +1106,11 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="9" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="166" fontId="19" fillId="0" borderId="9" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="165" fontId="19" fillId="0" borderId="9" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="9" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
@@ -1115,6 +1120,27 @@
     <xf numFmtId="14" fontId="19" fillId="0" borderId="9" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -11405,43 +11431,43 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>862393</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>131445</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Image 1" descr="Picture"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>2</col>
+      <colOff>862393</colOff>
+      <row>5</row>
+      <rowOff>131445</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
         <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
+      </blipFill>
+      <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
         <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -11743,20 +11769,21 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor theme="4" tint="0.3999755851924192"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:L43"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col width="12.77734375" customWidth="1" style="67" min="1" max="1"/>
-    <col width="13" customWidth="1" style="67" min="2" max="3"/>
+    <col width="13" customWidth="1" style="67" min="2" max="2"/>
     <col width="13" customWidth="1" style="67" min="3" max="3"/>
     <col width="15.77734375" customWidth="1" style="67" min="4" max="4"/>
     <col width="10" customWidth="1" style="67" min="5" max="5"/>
     <col width="15.77734375" customWidth="1" style="67" min="6" max="6"/>
-    <col width="11" customWidth="1" style="67" min="7" max="7"/>
+    <col width="15.77734375" customWidth="1" style="67" min="7" max="7"/>
     <col width="15.77734375" customWidth="1" style="67" min="8" max="8"/>
-    <col width="10" customWidth="1" style="67" min="9" max="9"/>
+    <col width="15.77734375" customWidth="1" style="67" min="9" max="9"/>
     <col width="15.77734375" customWidth="1" style="67" min="10" max="10"/>
     <col width="12" customWidth="1" style="67" min="11" max="11"/>
     <col width="13" customWidth="1" style="67" min="12" max="12"/>
@@ -11807,7 +11834,7 @@
         </is>
       </c>
       <c r="I5" s="29" t="n"/>
-      <c r="J5" s="1" t="inlineStr">
+      <c r="J5" s="188" t="inlineStr">
         <is>
           <t>Código</t>
         </is>
@@ -11826,7 +11853,7 @@
         </is>
       </c>
       <c r="I6" s="29" t="n"/>
-      <c r="J6" s="1" t="inlineStr">
+      <c r="J6" s="188" t="inlineStr">
         <is>
           <t>Versión</t>
         </is>
@@ -11845,7 +11872,7 @@
       <c r="G7" s="68" t="n"/>
       <c r="H7" s="68" t="n"/>
       <c r="I7" s="4" t="n"/>
-      <c r="J7" s="1" t="inlineStr">
+      <c r="J7" s="188" t="inlineStr">
         <is>
           <t>Fecha de Emisión</t>
         </is>
@@ -11864,7 +11891,7 @@
       <c r="G8" s="68" t="n"/>
       <c r="H8" s="68" t="n"/>
       <c r="I8" s="4" t="n"/>
-      <c r="J8" s="1" t="inlineStr">
+      <c r="J8" s="188" t="inlineStr">
         <is>
           <t>Página</t>
         </is>
@@ -11877,7 +11904,7 @@
       <c r="L8" s="32" t="n"/>
     </row>
     <row r="9" ht="28" customHeight="1" s="67">
-      <c r="A9" s="121" t="inlineStr">
+      <c r="A9" s="189" t="inlineStr">
         <is>
           <t>Lo que llega a la obra se cuenta contra lo pedido: así se sabe qué falta por entregar</t>
         </is>
@@ -11913,7 +11940,7 @@
       <c r="L10" s="17" t="n"/>
     </row>
     <row r="11" ht="21" customHeight="1" s="67">
-      <c r="A11" s="122" t="inlineStr">
+      <c r="A11" s="190" t="inlineStr">
         <is>
           <t>Proyecto / Obra</t>
         </is>
@@ -11924,7 +11951,7 @@
       <c r="E11" s="162" t="n"/>
       <c r="F11" s="162" t="n"/>
       <c r="G11" s="163" t="n"/>
-      <c r="H11" s="122" t="inlineStr">
+      <c r="H11" s="190" t="inlineStr">
         <is>
           <t>Ubicación</t>
         </is>
@@ -11935,7 +11962,7 @@
       <c r="L11" s="163" t="n"/>
     </row>
     <row r="12" ht="21" customHeight="1" s="67">
-      <c r="A12" s="122" t="inlineStr">
+      <c r="A12" s="190" t="inlineStr">
         <is>
           <t>Fecha de recepción</t>
         </is>
@@ -11946,7 +11973,7 @@
       <c r="E12" s="162" t="n"/>
       <c r="F12" s="162" t="n"/>
       <c r="G12" s="163" t="n"/>
-      <c r="H12" s="122" t="inlineStr">
+      <c r="H12" s="190" t="inlineStr">
         <is>
           <t>Entrada N°</t>
         </is>
@@ -11957,7 +11984,7 @@
       <c r="L12" s="163" t="n"/>
     </row>
     <row r="13" ht="21" customHeight="1" s="67">
-      <c r="A13" s="122" t="inlineStr">
+      <c r="A13" s="190" t="inlineStr">
         <is>
           <t>Orden de compra N°</t>
         </is>
@@ -11968,7 +11995,7 @@
       <c r="E13" s="162" t="n"/>
       <c r="F13" s="162" t="n"/>
       <c r="G13" s="163" t="n"/>
-      <c r="H13" s="122" t="inlineStr">
+      <c r="H13" s="190" t="inlineStr">
         <is>
           <t>Remisión o factura N°</t>
         </is>
@@ -11979,7 +12006,7 @@
       <c r="L13" s="163" t="n"/>
     </row>
     <row r="14" ht="21" customHeight="1" s="67">
-      <c r="A14" s="122" t="inlineStr">
+      <c r="A14" s="190" t="inlineStr">
         <is>
           <t>Proveedor</t>
         </is>
@@ -11990,7 +12017,7 @@
       <c r="E14" s="162" t="n"/>
       <c r="F14" s="162" t="n"/>
       <c r="G14" s="163" t="n"/>
-      <c r="H14" s="122" t="inlineStr">
+      <c r="H14" s="190" t="inlineStr">
         <is>
           <t>NIT</t>
         </is>
@@ -12001,7 +12028,7 @@
       <c r="L14" s="163" t="n"/>
     </row>
     <row r="15" ht="21" customHeight="1" s="67">
-      <c r="A15" s="122" t="inlineStr">
+      <c r="A15" s="190" t="inlineStr">
         <is>
           <t>Placa del vehículo</t>
         </is>
@@ -12012,7 +12039,7 @@
       <c r="E15" s="162" t="n"/>
       <c r="F15" s="162" t="n"/>
       <c r="G15" s="163" t="n"/>
-      <c r="H15" s="122" t="inlineStr">
+      <c r="H15" s="190" t="inlineStr">
         <is>
           <t>Hora</t>
         </is>
@@ -12041,12 +12068,12 @@
       <c r="L16" s="17" t="n"/>
     </row>
     <row r="17" ht="32" customHeight="1" s="67">
-      <c r="A17" s="42" t="inlineStr">
+      <c r="A17" s="191" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B17" s="124" t="inlineStr">
+      <c r="B17" s="192" t="inlineStr">
         <is>
           <t>Material y referencia</t>
         </is>
@@ -12054,32 +12081,32 @@
       <c r="C17" s="31" t="n"/>
       <c r="D17" s="31" t="n"/>
       <c r="E17" s="32" t="n"/>
-      <c r="F17" s="124" t="inlineStr">
+      <c r="F17" s="192" t="inlineStr">
         <is>
           <t>Unidad</t>
         </is>
       </c>
-      <c r="G17" s="124" t="inlineStr">
+      <c r="G17" s="192" t="inlineStr">
         <is>
           <t>Cantidad pedida</t>
         </is>
       </c>
-      <c r="H17" s="124" t="inlineStr">
+      <c r="H17" s="192" t="inlineStr">
         <is>
           <t>Recibido antes</t>
         </is>
       </c>
-      <c r="I17" s="124" t="inlineStr">
+      <c r="I17" s="192" t="inlineStr">
         <is>
           <t>Cantidad recibida</t>
         </is>
       </c>
-      <c r="J17" s="124" t="inlineStr">
+      <c r="J17" s="192" t="inlineStr">
         <is>
           <t>Saldo por recibir</t>
         </is>
       </c>
-      <c r="K17" s="124" t="inlineStr">
+      <c r="K17" s="192" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
@@ -12345,7 +12372,7 @@
       <c r="L33" s="17" t="n"/>
     </row>
     <row r="34" ht="21" customHeight="1" s="67">
-      <c r="A34" s="122" t="inlineStr">
+      <c r="A34" s="190" t="inlineStr">
         <is>
           <t>Resultado</t>
         </is>
@@ -12363,7 +12390,7 @@
       <c r="L34" s="163" t="n"/>
     </row>
     <row r="35" ht="21" customHeight="1" s="67">
-      <c r="A35" s="122" t="inlineStr">
+      <c r="A35" s="190" t="inlineStr">
         <is>
           <t>Ubicación de almacenamiento</t>
         </is>
@@ -12381,7 +12408,7 @@
       <c r="L35" s="163" t="n"/>
     </row>
     <row r="36" ht="45" customHeight="1" s="67">
-      <c r="A36" s="122" t="inlineStr">
+      <c r="A36" s="190" t="inlineStr">
         <is>
           <t>Novedades, daños o devoluciones</t>
         </is>
@@ -12399,7 +12426,7 @@
       <c r="L36" s="163" t="n"/>
     </row>
     <row r="37" ht="21" customHeight="1" s="67">
-      <c r="A37" s="122" t="inlineStr">
+      <c r="A37" s="190" t="inlineStr">
         <is>
           <t>¿Requiere inspección de calidad?</t>
         </is>
@@ -12435,7 +12462,7 @@
       <c r="L38" s="17" t="n"/>
     </row>
     <row r="39" ht="18" customHeight="1" s="67">
-      <c r="A39" s="130" t="inlineStr">
+      <c r="A39" s="193" t="inlineStr">
         <is>
           <t>RECIBE — ALMACENISTA</t>
         </is>
@@ -12443,7 +12470,7 @@
       <c r="B39" s="31" t="n"/>
       <c r="C39" s="31" t="n"/>
       <c r="D39" s="32" t="n"/>
-      <c r="E39" s="130" t="inlineStr">
+      <c r="E39" s="193" t="inlineStr">
         <is>
           <t>ENTREGA — PROVEEDOR / TRANSPORTADOR</t>
         </is>
@@ -12451,7 +12478,7 @@
       <c r="F39" s="31" t="n"/>
       <c r="G39" s="31" t="n"/>
       <c r="H39" s="32" t="n"/>
-      <c r="I39" s="130" t="inlineStr">
+      <c r="I39" s="193" t="inlineStr">
         <is>
           <t>REVISA — RESIDENTE DE OBRA</t>
         </is>
@@ -12461,7 +12488,7 @@
       <c r="L39" s="32" t="n"/>
     </row>
     <row r="40" ht="42" customHeight="1" s="67">
-      <c r="A40" s="18" t="inlineStr">
+      <c r="A40" s="194" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
@@ -12469,7 +12496,7 @@
       <c r="B40" s="17" t="n"/>
       <c r="C40" s="170" t="n"/>
       <c r="D40" s="172" t="n"/>
-      <c r="E40" s="18" t="inlineStr">
+      <c r="E40" s="194" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
@@ -12477,7 +12504,7 @@
       <c r="F40" s="17" t="n"/>
       <c r="G40" s="170" t="n"/>
       <c r="H40" s="172" t="n"/>
-      <c r="I40" s="18" t="inlineStr">
+      <c r="I40" s="194" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
@@ -12487,7 +12514,7 @@
       <c r="L40" s="172" t="n"/>
     </row>
     <row r="41" ht="21" customHeight="1" s="67">
-      <c r="A41" s="18" t="inlineStr">
+      <c r="A41" s="194" t="inlineStr">
         <is>
           <t>Nombre:</t>
         </is>
@@ -12495,7 +12522,7 @@
       <c r="B41" s="17" t="n"/>
       <c r="C41" s="170" t="n"/>
       <c r="D41" s="172" t="n"/>
-      <c r="E41" s="18" t="inlineStr">
+      <c r="E41" s="194" t="inlineStr">
         <is>
           <t>Nombre:</t>
         </is>
@@ -12503,7 +12530,7 @@
       <c r="F41" s="17" t="n"/>
       <c r="G41" s="170" t="n"/>
       <c r="H41" s="172" t="n"/>
-      <c r="I41" s="18" t="inlineStr">
+      <c r="I41" s="194" t="inlineStr">
         <is>
           <t>Nombre:</t>
         </is>
@@ -12513,7 +12540,7 @@
       <c r="L41" s="172" t="n"/>
     </row>
     <row r="42" ht="21" customHeight="1" s="67">
-      <c r="A42" s="18" t="inlineStr">
+      <c r="A42" s="194" t="inlineStr">
         <is>
           <t>Cargo:</t>
         </is>
@@ -12521,7 +12548,7 @@
       <c r="B42" s="17" t="n"/>
       <c r="C42" s="170" t="n"/>
       <c r="D42" s="172" t="n"/>
-      <c r="E42" s="18" t="inlineStr">
+      <c r="E42" s="194" t="inlineStr">
         <is>
           <t>Cargo:</t>
         </is>
@@ -12529,7 +12556,7 @@
       <c r="F42" s="17" t="n"/>
       <c r="G42" s="170" t="n"/>
       <c r="H42" s="172" t="n"/>
-      <c r="I42" s="18" t="inlineStr">
+      <c r="I42" s="194" t="inlineStr">
         <is>
           <t>Cargo:</t>
         </is>
@@ -12579,8 +12606,8 @@
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="K24:L24"/>
     <mergeCell ref="C14:G14"/>
+    <mergeCell ref="K26:L26"/>
     <mergeCell ref="J11:L11"/>
-    <mergeCell ref="K26:L26"/>
     <mergeCell ref="D1:L2"/>
     <mergeCell ref="A41:B41"/>
     <mergeCell ref="C41:D41"/>
